--- a/Lab 3/Sieve Data/Sieving Data.xlsx
+++ b/Lab 3/Sieve Data/Sieving Data.xlsx
@@ -12,21 +12,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Phi Range</t>
-  </si>
-  <si>
-    <t>Particle Size</t>
-  </si>
-  <si>
-    <t>Wentworth classification</t>
-  </si>
-  <si>
-    <t>Weight (g)</t>
-  </si>
-  <si>
-    <t>wt % of total sample</t>
   </si>
   <si>
     <t xml:space="preserve">&gt;4mm </t>
@@ -110,45 +98,35 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="3">
     <dxf>
       <font/>
       <fill>
         <patternFill patternType="none"/>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF356854"/>
-          <bgColor rgb="FF356854"/>
-        </patternFill>
       </fill>
       <border/>
     </dxf>
@@ -172,29 +150,11 @@
       </fill>
       <border/>
     </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF356854"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF356854"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF356854"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF356854"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="Sheet2-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle count="2" pivot="0" name="Sheet2-style">
+      <tableStyleElement dxfId="1" type="firstRowStripe"/>
+      <tableStyleElement dxfId="2" type="secondRowStripe"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -213,13 +173,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:E16" displayName="Table1" name="Table1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="B2:F10" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="5">
-    <tableColumn name="Phi Range" id="1"/>
-    <tableColumn name="Particle Size" id="2"/>
-    <tableColumn name="Wentworth classification" id="3"/>
-    <tableColumn name="Weight (g)" id="4"/>
-    <tableColumn name="wt % of total sample" id="5"/>
+    <tableColumn name="Column1" id="1"/>
+    <tableColumn name="Column2" id="2"/>
+    <tableColumn name="Column3" id="3"/>
+    <tableColumn name="Column4" id="4"/>
+    <tableColumn name="Column5" id="5"/>
   </tableColumns>
   <tableStyleInfo name="Sheet2-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
@@ -443,30 +403,13 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="22.63"/>
+    <col customWidth="1" min="1" max="1" width="22.63"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" ht="22.5" customHeight="1">
+    <row r="2">
       <c r="A2" s="2"/>
       <c r="B2" s="3" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="3">
@@ -475,13 +418,14 @@
       <c r="E2" s="4">
         <v>0.574</v>
       </c>
-    </row>
-    <row r="3" ht="22.5" customHeight="1">
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3">
       <c r="A3" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="5">
@@ -490,13 +434,14 @@
       <c r="E3" s="7">
         <v>0.089</v>
       </c>
-    </row>
-    <row r="4" ht="22.5" customHeight="1">
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4">
       <c r="A4" s="5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="5">
@@ -505,13 +450,14 @@
       <c r="E4" s="7">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="5" ht="22.5" customHeight="1">
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5">
       <c r="A5" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="5">
@@ -520,13 +466,14 @@
       <c r="E5" s="7">
         <v>0.027</v>
       </c>
-    </row>
-    <row r="6" ht="22.5" customHeight="1">
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6">
       <c r="A6" s="5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="5">
@@ -535,13 +482,14 @@
       <c r="E6" s="7">
         <v>0.037</v>
       </c>
-    </row>
-    <row r="7" ht="22.5" customHeight="1">
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7">
       <c r="A7" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="5">
@@ -550,13 +498,14 @@
       <c r="E7" s="7">
         <v>0.075</v>
       </c>
-    </row>
-    <row r="8" ht="22.5" customHeight="1">
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8">
       <c r="A8" s="5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5">
@@ -565,11 +514,12 @@
       <c r="E8" s="7">
         <v>0.086</v>
       </c>
-    </row>
-    <row r="9" ht="22.5" customHeight="1">
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9">
       <c r="A9" s="6"/>
       <c r="B9" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="5">
@@ -578,8 +528,9 @@
       <c r="E9" s="7">
         <v>0.069</v>
       </c>
-    </row>
-    <row r="10" ht="22.5" customHeight="1">
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -591,48 +542,7 @@
         <f t="shared" si="1"/>
         <v>0.997</v>
       </c>
-    </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-    </row>
-    <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-    </row>
-    <row r="16" ht="22.5" customHeight="1">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
+      <c r="F10" s="6"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/Lab 3/Sieve Data/Sieving Data.xlsx
+++ b/Lab 3/Sieve Data/Sieving Data.xlsx
@@ -4,7 +4,6 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Sheet2" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,9 +11,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Phi Range</t>
+  </si>
+  <si>
+    <t>Particle size</t>
+  </si>
+  <si>
+    <t>Wentworth</t>
+  </si>
+  <si>
+    <t>Weight (g)</t>
+  </si>
+  <si>
+    <t>wt %</t>
   </si>
   <si>
     <t xml:space="preserve">&gt;4mm </t>
@@ -73,15 +84,26 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8F9"/>
+        <bgColor rgb="FFF6F8F9"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -90,33 +112,51 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -152,7 +192,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="2" pivot="0" name="Sheet2-style">
+    <tableStyle count="2" pivot="0" name="Sheet1-style">
       <tableStyleElement dxfId="1" type="firstRowStripe"/>
       <tableStyleElement dxfId="2" type="secondRowStripe"/>
     </tableStyle>
@@ -161,10 +201,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -181,7 +217,7 @@
     <tableColumn name="Column4" id="4"/>
     <tableColumn name="Column5" id="5"/>
   </tableColumns>
-  <tableStyleInfo name="Sheet2-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Sheet1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -390,159 +426,157 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-  </sheetData>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="22.63"/>
-  </cols>
-  <sheetData>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1"/>
+    </row>
     <row r="2">
-      <c r="A2" s="2"/>
-      <c r="B2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="2">
         <v>563.2</v>
       </c>
       <c r="E2" s="4">
         <v>0.574</v>
       </c>
-      <c r="F2" s="4"/>
+      <c r="F2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="5">
+      <c r="A3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="9">
         <v>87.6</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="10">
         <v>0.089</v>
       </c>
-      <c r="F3" s="7"/>
+      <c r="F3" s="11"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="5">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="13">
         <v>38.9</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="14">
         <v>0.04</v>
       </c>
-      <c r="F4" s="7"/>
+      <c r="F4" s="5"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="5">
+      <c r="A5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="9">
         <v>26.1</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="10">
         <v>0.027</v>
       </c>
-      <c r="F5" s="7"/>
+      <c r="F5" s="11"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="5">
+      <c r="A6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="13">
         <v>36.4</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="14">
         <v>0.037</v>
       </c>
-      <c r="F6" s="7"/>
+      <c r="F6" s="5"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="5">
+      <c r="A7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="9">
         <v>74.0</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="10">
         <v>0.075</v>
       </c>
-      <c r="F7" s="7"/>
+      <c r="F7" s="11"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="5">
+      <c r="A8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="13">
         <v>84.2</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="14">
         <v>0.086</v>
       </c>
-      <c r="F8" s="7"/>
+      <c r="F8" s="5"/>
     </row>
     <row r="9">
-      <c r="A9" s="6"/>
-      <c r="B9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="5">
+      <c r="A9" s="1"/>
+      <c r="B9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="9">
         <v>67.9</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="10">
         <v>0.069</v>
       </c>
-      <c r="F9" s="7"/>
+      <c r="F9" s="11"/>
     </row>
     <row r="10">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6">
+      <c r="A10" s="1"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="13">
         <f t="shared" ref="D10:E10" si="1">SUM(D2:D9)</f>
         <v>978.3</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="14">
         <f t="shared" si="1"/>
         <v>0.997</v>
       </c>
-      <c r="F10" s="6"/>
+      <c r="F10" s="3"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
